--- a/exports/ADANIPORTS_full_report.xlsx
+++ b/exports/ADANIPORTS_full_report.xlsx
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -6398,16 +6398,16 @@
         <v>1674.2</v>
       </c>
       <c r="E59" t="n">
-        <v>1746.7</v>
+        <v>1755</v>
       </c>
       <c r="F59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" t="n">
         <v>6.43</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.2</v>
+        <v>-1.74</v>
       </c>
       <c r="I59" t="n">
         <v>0.17</v>

--- a/exports/ADANIPORTS_full_report.xlsx
+++ b/exports/ADANIPORTS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.64</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>762.95</v>
+        <v>739.7</v>
       </c>
       <c r="I2" t="n">
         <v>740.0333823714143</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.57</v>
+        <v>0.41</v>
       </c>
       <c r="L2" t="n">
         <v>1.11</v>
@@ -555,7 +578,7 @@
         <v>0.26</v>
       </c>
       <c r="N2" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
         <v>0.29</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.68</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44607.55208333334</v>
+        <v>44608.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>719.05</v>
+        <v>746.7</v>
       </c>
       <c r="I3" t="n">
         <v>744.5240079998678</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>2.79</v>
+        <v>-0.95</v>
       </c>
       <c r="L3" t="n">
         <v>2.98</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>8.17</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>712</v>
+        <v>690.2</v>
       </c>
       <c r="I4" t="n">
         <v>692.6383015938106</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.65</v>
+        <v>-7.57</v>
       </c>
       <c r="L4" t="n">
-        <v>4.98</v>
+        <v>7.92</v>
       </c>
       <c r="M4" t="n">
-        <v>0.79</v>
+        <v>1.97</v>
       </c>
       <c r="N4" t="n">
         <v>2.26</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>7.31</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>714</v>
+        <v>729.5</v>
       </c>
       <c r="I5" t="n">
         <v>718.0890105197346</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.45</v>
+        <v>-5.69</v>
       </c>
       <c r="L5" t="n">
-        <v>4.98</v>
+        <v>6.87</v>
       </c>
       <c r="M5" t="n">
         <v>2.68</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.76</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>856.4</v>
+        <v>828.95</v>
       </c>
       <c r="I6" t="n">
         <v>833.609569168146</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K6" t="n">
-        <v>17.4</v>
+        <v>13.63</v>
       </c>
       <c r="L6" t="n">
         <v>1.82</v>
@@ -783,7 +854,7 @@
         <v>0.88</v>
       </c>
       <c r="N6" t="n">
-        <v>4.02</v>
+        <v>5.19</v>
       </c>
       <c r="O6" t="n">
         <v>2.17</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.92</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44749.55208333334</v>
+        <v>44750.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>703</v>
+        <v>711.25</v>
       </c>
       <c r="I7" t="n">
         <v>705.5377548578788</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>65</v>
       </c>
       <c r="K7" t="n">
-        <v>15.19</v>
+        <v>14.2</v>
       </c>
       <c r="L7" t="n">
         <v>4.25</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>5.16</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44796.55208333334</v>
+        <v>44797.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>836</v>
+        <v>820.85</v>
       </c>
       <c r="I8" t="n">
         <v>827.8642679959231</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K8" t="n">
-        <v>17.54</v>
+        <v>15.41</v>
       </c>
       <c r="L8" t="n">
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>3.45</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.16</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44812.38541666666</v>
+        <v>44812.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>870.1</v>
+        <v>882.9</v>
       </c>
       <c r="I9" t="n">
         <v>880.7851923616026</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-6</v>
+        <v>-7.56</v>
       </c>
       <c r="L9" t="n">
-        <v>7.58</v>
+        <v>8.18</v>
       </c>
       <c r="M9" t="n">
         <v>0.93</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.38541666666</v>
+        <v>44827.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>923.55</v>
+        <v>912.7</v>
       </c>
       <c r="I10" t="n">
         <v>920.4345461502506</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>3.38</v>
       </c>
       <c r="L10" t="n">
         <v>1.53</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.72</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>826.7</v>
+        <v>840.9</v>
       </c>
       <c r="I11" t="n">
         <v>834.9943882959149</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K11" t="n">
-        <v>9.42</v>
+        <v>7.87</v>
       </c>
       <c r="L11" t="n">
         <v>1.65</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.41</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>876.7</v>
+        <v>858.9</v>
       </c>
       <c r="I12" t="n">
         <v>863.7110389019634</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>44.83333333333334</v>
+        <v>45</v>
       </c>
       <c r="K12" t="n">
-        <v>4.26</v>
+        <v>2.14</v>
       </c>
       <c r="L12" t="n">
         <v>2.07</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.98</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44965.38541666666</v>
+        <v>44965.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>591.25</v>
+        <v>602.9</v>
       </c>
       <c r="I13" t="n">
         <v>593.2053790779448</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K13" t="n">
-        <v>31.16</v>
+        <v>29.81</v>
       </c>
       <c r="L13" t="n">
         <v>4.32</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>23.56</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>637.55</v>
+        <v>628.05</v>
       </c>
       <c r="I14" t="n">
         <v>634.8530961580019</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>44</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>5.75</v>
+        <v>4.17</v>
       </c>
       <c r="L14" t="n">
         <v>11.45</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.75</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45021.55208333334</v>
+        <v>45022.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>635.95</v>
+        <v>649.35</v>
       </c>
       <c r="I15" t="n">
         <v>647.9117597387151</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.26</v>
+        <v>-3.39</v>
       </c>
       <c r="L15" t="n">
         <v>4.13</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>684.6</v>
+        <v>673.65</v>
       </c>
       <c r="I16" t="n">
         <v>678.0537943272029</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K16" t="n">
-        <v>5.43</v>
+        <v>3.74</v>
       </c>
       <c r="L16" t="n">
         <v>2.74</v>
@@ -1353,7 +1544,7 @@
         <v>0.83</v>
       </c>
       <c r="N16" t="n">
-        <v>1.86</v>
+        <v>3.16</v>
       </c>
       <c r="O16" t="n">
         <v>0.83</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>690</v>
+        <v>734.2</v>
       </c>
       <c r="I17" t="n">
         <v>698.548256113812</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.43</v>
+        <v>-8.99</v>
       </c>
       <c r="L17" t="n">
-        <v>3.04</v>
+        <v>11.78</v>
       </c>
       <c r="M17" t="n">
-        <v>0.74</v>
+        <v>1.29</v>
       </c>
       <c r="N17" t="n">
-        <v>4.07</v>
+        <v>6.12</v>
       </c>
       <c r="O17" t="n">
         <v>-3.16</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.77</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>745</v>
+        <v>718.4</v>
       </c>
       <c r="I18" t="n">
         <v>725.8254373062055</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>1.47</v>
+        <v>-2.15</v>
       </c>
       <c r="L18" t="n">
         <v>5.48</v>
@@ -1467,7 +1682,7 @@
         <v>1.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.33</v>
+        <v>4.36</v>
       </c>
       <c r="O18" t="n">
         <v>6.12</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.52</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45105.38541666666</v>
+        <v>45105.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>744.7</v>
+        <v>755</v>
       </c>
       <c r="I19" t="n">
         <v>749.6346062037762</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.66</v>
+        <v>-5.09</v>
       </c>
       <c r="L19" t="n">
-        <v>3.83</v>
+        <v>5.62</v>
       </c>
       <c r="M19" t="n">
         <v>0.59</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.76</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45163.38541666666</v>
+        <v>45163.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>809.8</v>
+        <v>806</v>
       </c>
       <c r="I20" t="n">
         <v>807.5727430929859</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>57.83333333333334</v>
+        <v>58</v>
       </c>
       <c r="K20" t="n">
-        <v>7.26</v>
+        <v>6.75</v>
       </c>
       <c r="L20" t="n">
         <v>6.23</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>6.49</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45177.55208333334</v>
+        <v>45180.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>823</v>
+        <v>879.5</v>
       </c>
       <c r="I21" t="n">
         <v>842.3655592643864</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.11</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>3.35</v>
+        <v>10.07</v>
       </c>
       <c r="M21" t="n">
-        <v>1.24</v>
+        <v>2.07</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>7.36</v>
       </c>
       <c r="O21" t="n">
         <v>-2.11</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>8.06</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45187.38541666666</v>
+        <v>45187.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>839.2</v>
+        <v>830.45</v>
       </c>
       <c r="I22" t="n">
         <v>830.882282708613</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.58</v>
+        <v>-5.58</v>
       </c>
       <c r="L22" t="n">
-        <v>5.06</v>
+        <v>5.84</v>
       </c>
       <c r="M22" t="n">
         <v>-0</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.89</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>795</v>
+        <v>802.75</v>
       </c>
       <c r="I23" t="n">
         <v>797.1889533257456</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>4.27</v>
+        <v>3.34</v>
       </c>
       <c r="L23" t="n">
         <v>1.81</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4.33</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45253.55208333334</v>
+        <v>45254.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>793.2</v>
+        <v>785.7</v>
       </c>
       <c r="I24" t="n">
         <v>786.4949201123609</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.19</v>
+        <v>-2.12</v>
       </c>
       <c r="L24" t="n">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="M24" t="n">
         <v>0.28</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.23</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45254.55208333334</v>
+        <v>45258.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>801</v>
+        <v>843.05</v>
       </c>
       <c r="I25" t="n">
         <v>818.9131133982405</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.95</v>
+        <v>-7.3</v>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>8.74</v>
       </c>
       <c r="M25" t="n">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="N25" t="n">
-        <v>0.98</v>
+        <v>4.93</v>
       </c>
       <c r="O25" t="n">
         <v>0.98</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1045.2</v>
+        <v>1006.5</v>
       </c>
       <c r="I26" t="n">
         <v>1025.910976098727</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>23.98</v>
+        <v>19.39</v>
       </c>
       <c r="L26" t="n">
         <v>4.39</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.76</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45293.38541666666</v>
+        <v>45293.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1055.55</v>
+        <v>1078.55</v>
       </c>
       <c r="I27" t="n">
         <v>1073.992414445438</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.87</v>
+        <v>-7.16</v>
       </c>
       <c r="L27" t="n">
-        <v>6.31</v>
+        <v>7.59</v>
       </c>
       <c r="M27" t="n">
         <v>0.97</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.95</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1155.15</v>
+        <v>1142</v>
       </c>
       <c r="I28" t="n">
         <v>1146.19159988012</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
-        <v>7.1</v>
+        <v>5.88</v>
       </c>
       <c r="L28" t="n">
         <v>2.21</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.59</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45320.38541666666</v>
+        <v>45320.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1192.8</v>
+        <v>1194.4</v>
       </c>
       <c r="I29" t="n">
         <v>1193.115358712133</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.45</v>
+        <v>-4.59</v>
       </c>
       <c r="L29" t="n">
-        <v>4.79</v>
+        <v>5.51</v>
       </c>
       <c r="M29" t="n">
         <v>0.35</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.97</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1297.35</v>
+        <v>1229.9</v>
       </c>
       <c r="I30" t="n">
         <v>1280.474667113705</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>8.619999999999999</v>
+        <v>2.97</v>
       </c>
       <c r="L30" t="n">
         <v>1.12</v>
@@ -2151,7 +2510,7 @@
         <v>0.71</v>
       </c>
       <c r="N30" t="n">
-        <v>2.74</v>
+        <v>6.19</v>
       </c>
       <c r="O30" t="n">
         <v>3.77</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.66</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45377.38541666666</v>
+        <v>45377.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1300</v>
+        <v>1305</v>
       </c>
       <c r="I31" t="n">
         <v>1302.043452224676</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.7</v>
+        <v>-6.11</v>
       </c>
       <c r="L31" t="n">
-        <v>6.35</v>
+        <v>6.84</v>
       </c>
       <c r="M31" t="n">
         <v>1.29</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.44</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1347</v>
+        <v>1318.45</v>
       </c>
       <c r="I32" t="n">
         <v>1328.071605430661</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>3.22</v>
+        <v>1.03</v>
       </c>
       <c r="L32" t="n">
         <v>0.42</v>
       </c>
       <c r="M32" t="n">
-        <v>0.21</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="O32" t="n">
         <v>2.22</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.86</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45425.55208333334</v>
+        <v>45426.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1305.1</v>
+        <v>1335.95</v>
       </c>
       <c r="I33" t="n">
         <v>1324.454166453531</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K33" t="n">
-        <v>1.01</v>
+        <v>-1.33</v>
       </c>
       <c r="L33" t="n">
         <v>2.7</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1591</v>
+        <v>1295</v>
       </c>
       <c r="I34" t="n">
         <v>1447.458622522783</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>19.09</v>
+        <v>-3.07</v>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>11.07</v>
       </c>
       <c r="M34" t="n">
-        <v>0.89</v>
+        <v>2.07</v>
       </c>
       <c r="N34" t="n">
-        <v>2.24</v>
+        <v>21.75</v>
       </c>
       <c r="O34" t="n">
         <v>2.1</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>24.51</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1490</v>
+        <v>1542.7</v>
       </c>
       <c r="I35" t="n">
         <v>1518.542749042424</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K35" t="n">
-        <v>-15.06</v>
+        <v>-19.13</v>
       </c>
       <c r="L35" t="n">
         <v>20.31</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.94</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1586.05</v>
+        <v>1489.1</v>
       </c>
       <c r="I36" t="n">
         <v>1518.089973323497</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>2.81</v>
+        <v>-3.47</v>
       </c>
       <c r="L36" t="n">
-        <v>3.42</v>
+        <v>4.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0.57</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0.18</v>
+        <v>5.76</v>
       </c>
       <c r="O36" t="n">
         <v>3.41</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45561.38541666666</v>
+        <v>45561.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1453.55</v>
+        <v>1474.1</v>
       </c>
       <c r="I37" t="n">
         <v>1465.226733447233</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K37" t="n">
-        <v>2.39</v>
+        <v>1.01</v>
       </c>
       <c r="L37" t="n">
         <v>4.99</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>4.72</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45569.38541666666</v>
+        <v>45569.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1419.6</v>
+        <v>1410</v>
       </c>
       <c r="I38" t="n">
         <v>1415.05265577319</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.7</v>
+        <v>-4.35</v>
       </c>
       <c r="L38" t="n">
-        <v>4.61</v>
+        <v>4.74</v>
       </c>
       <c r="M38" t="n">
         <v>0.71</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.04</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1377</v>
+        <v>1408.6</v>
       </c>
       <c r="I39" t="n">
         <v>1384.890299358435</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>2.34</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
         <v>1.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.07</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45600.55208333334</v>
+        <v>45601.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1349</v>
+        <v>1303.6</v>
       </c>
       <c r="I40" t="n">
         <v>1313.007711093654</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.23</v>
+        <v>-7.45</v>
       </c>
       <c r="L40" t="n">
-        <v>5.15</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
         <v>0.01</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.82</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45628.55208333334</v>
+        <v>45629.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1215.5</v>
+        <v>1281.85</v>
       </c>
       <c r="I41" t="n">
         <v>1234.477430167293</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
-        <v>6.76</v>
+        <v>1.67</v>
       </c>
       <c r="L41" t="n">
         <v>6.01</v>
@@ -2778,7 +3269,7 @@
         <v>4.08</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>5.88</v>
       </c>
       <c r="O41" t="n">
         <v>-1.48</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>12.23</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>1192.3</v>
+        <v>1181.3</v>
       </c>
       <c r="I42" t="n">
         <v>1181.331823196777</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.99</v>
+        <v>-7.84</v>
       </c>
       <c r="L42" t="n">
-        <v>7.56</v>
+        <v>8.24</v>
       </c>
       <c r="M42" t="n">
         <v>1.93</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>5.81</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45652.38541666666</v>
+        <v>45652.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1203.25</v>
+        <v>1243.95</v>
       </c>
       <c r="I43" t="n">
         <v>1241.552713470178</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.86</v>
+        <v>-5.3</v>
       </c>
       <c r="L43" t="n">
-        <v>2.17</v>
+        <v>5.73</v>
       </c>
       <c r="M43" t="n">
         <v>0.73</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.01</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1197.8</v>
+        <v>1175.8</v>
       </c>
       <c r="I44" t="n">
         <v>1179.245828472995</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.71</v>
+        <v>-5.48</v>
       </c>
       <c r="L44" t="n">
-        <v>3.77</v>
+        <v>6.23</v>
       </c>
       <c r="M44" t="n">
         <v>0.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.22</v>
+        <v>2.91</v>
       </c>
       <c r="O44" t="n">
         <v>5.24</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>6.14</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1128.3</v>
+        <v>1156.95</v>
       </c>
       <c r="I45" t="n">
         <v>1139.960048899218</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>4.04</v>
+        <v>1.6</v>
       </c>
       <c r="L45" t="n">
         <v>2.13</v>
       </c>
       <c r="M45" t="n">
-        <v>0.95</v>
+        <v>4.58</v>
       </c>
       <c r="N45" t="n">
         <v>4.98</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.19</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1110.9</v>
+        <v>1085.05</v>
       </c>
       <c r="I46" t="n">
         <v>1089.18383921214</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.98</v>
+        <v>-6.21</v>
       </c>
       <c r="L46" t="n">
-        <v>4.58</v>
+        <v>6.55</v>
       </c>
       <c r="M46" t="n">
         <v>0.02</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45693.55208333334</v>
+        <v>45694.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1147.5</v>
+        <v>1161.15</v>
       </c>
       <c r="I47" t="n">
         <v>1149.97387421393</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.76</v>
+        <v>-7.01</v>
       </c>
       <c r="L47" t="n">
-        <v>6.44</v>
+        <v>7.12</v>
       </c>
       <c r="M47" t="n">
         <v>1.21</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>7.56</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1107.9</v>
+        <v>1062.8</v>
       </c>
       <c r="I48" t="n">
         <v>1091.316359396233</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.59</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>5.36</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>0.52</v>
       </c>
       <c r="N48" t="n">
-        <v>1.83</v>
+        <v>4.17</v>
       </c>
       <c r="O48" t="n">
         <v>1.62</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.4</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45721.38541666666</v>
+        <v>45721.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1107</v>
+        <v>1112.45</v>
       </c>
       <c r="I49" t="n">
         <v>1109.653677386068</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.16</v>
+        <v>-4.67</v>
       </c>
       <c r="L49" t="n">
         <v>5.95</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>6.49</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1152</v>
+        <v>1088.3</v>
       </c>
       <c r="I50" t="n">
         <v>1146.89943370116</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K50" t="n">
-        <v>3.56</v>
+        <v>-2.17</v>
       </c>
       <c r="L50" t="n">
-        <v>0.95</v>
+        <v>6.38</v>
       </c>
       <c r="M50" t="n">
-        <v>0.53</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N50" t="n">
         <v>4.1</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.59</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1162</v>
+        <v>1209.6</v>
       </c>
       <c r="I51" t="n">
         <v>1170.934101676776</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.77</v>
+        <v>-11.15</v>
       </c>
       <c r="L51" t="n">
-        <v>7.53</v>
+        <v>12.64</v>
       </c>
       <c r="M51" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="N51" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="O51" t="n">
         <v>-2.86</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1441</v>
+        <v>1402.1</v>
       </c>
       <c r="I52" t="n">
         <v>1422.724356788872</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K52" t="n">
-        <v>19.13</v>
+        <v>15.91</v>
       </c>
       <c r="L52" t="n">
         <v>2.53</v>
       </c>
       <c r="M52" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="N52" t="n">
         <v>3.8</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.03</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1351.1</v>
+        <v>1404.5</v>
       </c>
       <c r="I53" t="n">
         <v>1400.694376861518</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>3.64</v>
+        <v>-0.17</v>
       </c>
       <c r="L53" t="n">
         <v>1.55</v>
       </c>
       <c r="M53" t="n">
-        <v>0.04</v>
+        <v>3.26</v>
       </c>
       <c r="N53" t="n">
-        <v>1.19</v>
+        <v>3.18</v>
       </c>
       <c r="O53" t="n">
         <v>-2.39</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.33</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1422.5</v>
+        <v>1410.6</v>
       </c>
       <c r="I54" t="n">
         <v>1413.012063225513</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K54" t="n">
-        <v>1.28</v>
+        <v>0.43</v>
       </c>
       <c r="L54" t="n">
         <v>1.38</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>3.68</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45888.38541666666</v>
+        <v>45888.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1356.1</v>
+        <v>1370</v>
       </c>
       <c r="I55" t="n">
         <v>1361.043015289572</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="L55" t="n">
         <v>1.09</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.47</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1407.8</v>
+        <v>1391.4</v>
       </c>
       <c r="I56" t="n">
         <v>1391.478605234557</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K56" t="n">
-        <v>2.76</v>
+        <v>1.56</v>
       </c>
       <c r="L56" t="n">
         <v>4.89</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>4.78</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1425</v>
+        <v>1450.3</v>
       </c>
       <c r="I57" t="n">
         <v>1442.536944294002</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.41</v>
+        <v>-4.23</v>
       </c>
       <c r="L57" t="n">
-        <v>3.65</v>
+        <v>4.66</v>
       </c>
       <c r="M57" t="n">
         <v>0.37</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>4.38</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45954.55208333334</v>
+        <v>45957.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1426.2</v>
+        <v>1416.9</v>
       </c>
       <c r="I58" t="n">
         <v>1424.047523941942</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.66</v>
+        <v>-2.3</v>
       </c>
       <c r="L58" t="n">
-        <v>1.93</v>
+        <v>2.78</v>
       </c>
       <c r="M58" t="n">
         <v>0.01</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>4.26</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45972.38541666666</v>
+        <v>45972.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1445</v>
+        <v>1473.9</v>
       </c>
       <c r="I59" t="n">
         <v>1467.373986757997</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.98</v>
+        <v>-4.02</v>
       </c>
       <c r="L59" t="n">
-        <v>3.49</v>
+        <v>4.17</v>
       </c>
       <c r="M59" t="n">
         <v>0.82</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.14</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46017.55208333334</v>
+        <v>46020.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1487.1</v>
+        <v>1462.8</v>
       </c>
       <c r="I60" t="n">
         <v>1478.796317169205</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9</v>
+        <v>-0.75</v>
       </c>
       <c r="L60" t="n">
         <v>1.96</v>
@@ -3861,7 +4580,7 @@
         <v>0.33</v>
       </c>
       <c r="N60" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="O60" t="n">
         <v>2.03</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>3.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46051.38541666666</v>
+        <v>46051.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1390.5</v>
+        <v>1417.1</v>
       </c>
       <c r="I61" t="n">
         <v>1416.297644559352</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>4.94</v>
+        <v>3.12</v>
       </c>
       <c r="L61" t="n">
         <v>2.32</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>6.99</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1519.8</v>
+        <v>1438.5</v>
       </c>
       <c r="I62" t="n">
         <v>1486.613086753549</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>7.25</v>
+        <v>1.51</v>
       </c>
       <c r="L62" t="n">
         <v>6.5</v>
       </c>
       <c r="M62" t="n">
-        <v>0.39</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
         <v>4.87</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>8.41</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1382</v>
+        <v>1456.4</v>
       </c>
       <c r="I63" t="n">
         <v>1404.116545816552</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K63" t="n">
-        <v>3.93</v>
+        <v>-1.24</v>
       </c>
       <c r="L63" t="n">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="M63" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="N63" t="n">
         <v>5.4</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.79</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1833.5</v>
+        <v>1800.9</v>
       </c>
       <c r="I64" t="n">
         <v>1802.570486287173</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>91</v>
+        <v>91.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>25.89</v>
+        <v>23.65</v>
       </c>
       <c r="L64" t="n">
         <v>2.83</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.18</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1696.8</v>
+        <v>1711.8</v>
       </c>
       <c r="I65" t="n">
         <v>1710.355312370291</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>5.78</v>
+        <v>4.95</v>
       </c>
       <c r="L65" t="n">
         <v>3.27</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>3.64</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46265.38541666666</v>
+        <v>46265.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1664.7</v>
+        <v>1650.1</v>
       </c>
       <c r="I66" t="n">
         <v>1656.057553930551</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.75</v>
+        <v>-3.6</v>
       </c>
       <c r="L66" t="n">
-        <v>3.21</v>
+        <v>4.41</v>
       </c>
       <c r="M66" t="n">
         <v>0.12</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.02</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1707.5</v>
+        <v>1769.9</v>
       </c>
       <c r="I67" t="n">
         <v>1708.868397979549</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.48</v>
+        <v>-7.26</v>
       </c>
       <c r="L67" t="n">
-        <v>4.05</v>
+        <v>7.36</v>
       </c>
       <c r="M67" t="n">
         <v>1.47</v>
       </c>
       <c r="N67" t="n">
-        <v>1.8</v>
+        <v>3.38</v>
       </c>
       <c r="O67" t="n">
         <v>-3.23</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.04</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1788.9</v>
+        <v>1739.9</v>
       </c>
       <c r="I68" t="n">
         <v>1746.67864051094</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>1.07</v>
+        <v>-1.7</v>
       </c>
       <c r="L68" t="n">
         <v>3.61</v>
@@ -4317,7 +5132,7 @@
         <v>0.62</v>
       </c>
       <c r="N68" t="n">
-        <v>2.31</v>
+        <v>2.68</v>
       </c>
       <c r="O68" t="n">
         <v>3.38</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>42</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7324,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7344,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7374,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7404,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.63</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.47</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.73</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7434,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.16</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7444,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.7</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.98</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7464,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.61</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="21">
@@ -6649,7 +7484,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7494,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7504,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7514,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.36</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7524,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.53</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7534,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.79</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7544,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
